--- a/Excel_Data/PD20/XF Real-Time ATP Rate Assay pd20,rv,healthy  02.06.26    WITHHHHHH-XF ATP Rate Assay-ATP Production (Basal Rates).xlsx
+++ b/Excel_Data/PD20/XF Real-Time ATP Rate Assay pd20,rv,healthy  02.06.26    WITHHHHHH-XF ATP Rate Assay-ATP Production (Basal Rates).xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10308"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leonardharris/PycharmProjects/FA_Metabolism/Excel_Data/PD20/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A383AB9-EB11-FC48-85EF-87448CAB1578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="1000" windowWidth="15000" windowHeight="10000"/>
+    <workbookView xWindow="-39420" yWindow="4560" windowWidth="15000" windowHeight="10000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ATP Production (Basal Rates)" sheetId="1" r:id="rId1"/>
@@ -46,9 +52,6 @@
     <t>RV</t>
   </si>
   <si>
-    <t>XF Real-Time ATP Rate Assay pd20,rv,healthy 2.6.2026 WITHHHHHH</t>
-  </si>
-  <si>
     <t>PD20</t>
   </si>
   <si>
@@ -140,26 +143,29 @@
   </si>
   <si>
     <t>glycoATP Production Rate</t>
+  </si>
+  <si>
+    <t>XF Real-Time ATP Rate Assay pd20,rv,healthy 02.06.26 WITHHHHHH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -172,7 +178,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border outline="0">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -183,13 +189,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" relativeIndent="0" readingOrder="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -197,6 +202,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -484,380 +497,376 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" customWidth="1"/>
-    <col min="2" max="2" width="28.5703125" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625"/>
+    <col min="1" max="1" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="28.5" customWidth="1"/>
+    <col min="3" max="3" width="21.5" customWidth="1"/>
+    <col min="4" max="4" width="28.5" customWidth="1"/>
+    <col min="5" max="5" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="D9" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>14.5395236596188</v>
       </c>
-      <c r="D10" s="3">
-        <v>13.6890474834126</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="D10" s="2">
+        <v>13.689047483412599</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>11.6504588408215</v>
       </c>
-      <c r="D11" s="3">
-        <v>8.35604788264597</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="D11" s="2">
+        <v>8.3560478826459708</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2">
+        <v>12.759919859793699</v>
+      </c>
+      <c r="D12" s="2">
+        <v>10.599227071177699</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="3">
-        <v>12.7599198597937</v>
-      </c>
-      <c r="D12" s="3">
-        <v>10.5992270711777</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="2">
+        <v>13.7099949761618</v>
+      </c>
+      <c r="D13" s="2">
+        <v>15.3711314626138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="2">
+        <v>14.0480376902504</v>
+      </c>
+      <c r="D14" s="2">
+        <v>15.5796914681875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="2">
+        <v>12.4167279590108</v>
+      </c>
+      <c r="D15" s="2">
+        <v>11.7149140130561</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="2">
+        <v>8.63494925313252</v>
+      </c>
+      <c r="D16" s="2">
+        <v>13.3847944243689</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2">
+        <v>9.8695323761209792</v>
+      </c>
+      <c r="D17" s="2">
+        <v>11.484482932259599</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="2">
+        <v>7.7360472908703102</v>
+      </c>
+      <c r="D18" s="2">
+        <v>14.692807018093401</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="3">
-        <v>13.7099949761618</v>
-      </c>
-      <c r="D13" s="3">
-        <v>15.3711314626138</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="3">
-        <v>14.0480376902504</v>
-      </c>
-      <c r="D14" s="3">
-        <v>15.5796914681875</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="C19" s="2">
+        <v>10.3959278838194</v>
+      </c>
+      <c r="D19" s="2">
+        <v>12.062615273959199</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="3">
-        <v>12.4167279590108</v>
-      </c>
-      <c r="D15" s="3">
-        <v>11.7149140130561</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="C20" s="2">
+        <v>9.2770921300713596</v>
+      </c>
+      <c r="D20" s="2">
+        <v>8.7931051669082905</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="3">
-        <v>8.63494925313252</v>
-      </c>
-      <c r="D16" s="3">
-        <v>13.3847944243689</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
+      <c r="C21" s="2">
+        <v>7.5681149274736201</v>
+      </c>
+      <c r="D21" s="2">
+        <v>11.405282314428501</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="3">
-        <v>9.86953237612098</v>
-      </c>
-      <c r="D17" s="3">
-        <v>11.4844829322596</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="3">
-        <v>7.73604729087031</v>
-      </c>
-      <c r="D18" s="3">
-        <v>14.6928070180934</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="2">
+        <v>8.5346523295642598</v>
+      </c>
+      <c r="D22" s="2">
+        <v>11.303985516584</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="2">
+        <v>4.5893946262546201</v>
+      </c>
+      <c r="D23" s="2">
+        <v>23.578479701457098</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="3">
-        <v>10.3959278838194</v>
-      </c>
-      <c r="D19" s="3">
-        <v>12.0626152739592</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="C24" s="2">
+        <v>6.8823660897499801</v>
+      </c>
+      <c r="D24" s="2">
+        <v>24.1667445319998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="2">
+        <v>5.9705463217463501</v>
+      </c>
+      <c r="D25" s="2">
+        <v>24.548199402785301</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="3">
-        <v>9.27709213007136</v>
-      </c>
-      <c r="D20" s="3">
-        <v>8.79310516690829</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="3">
-        <v>7.56811492747362</v>
-      </c>
-      <c r="D21" s="3">
-        <v>11.4052823144285</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="C26" s="2">
+        <v>7.8845449526269604</v>
+      </c>
+      <c r="D26" s="2">
+        <v>21.357762646965799</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="2">
+        <v>7.33062629158339</v>
+      </c>
+      <c r="D27" s="2">
+        <v>27.5787413103562</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="3">
-        <v>8.53465232956426</v>
-      </c>
-      <c r="D22" s="3">
-        <v>11.303985516584</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="3">
-        <v>4.58939462625462</v>
-      </c>
-      <c r="D23" s="3">
-        <v>23.5784797014571</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="3">
-        <v>6.88236608974998</v>
-      </c>
-      <c r="D24" s="3">
-        <v>24.1667445319998</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="3">
-        <v>5.97054632174635</v>
-      </c>
-      <c r="D25" s="3">
-        <v>24.5481994027853</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="3">
-        <v>7.88454495262696</v>
-      </c>
-      <c r="D26" s="3">
-        <v>21.3577626469658</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="3">
-        <v>7.33062629158339</v>
-      </c>
-      <c r="D27" s="3">
-        <v>27.5787413103562</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="2">
+        <v>3.4732269602203298</v>
+      </c>
+      <c r="D28" s="2">
+        <v>25.936936200373999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="3">
-        <v>3.47322696022033</v>
-      </c>
-      <c r="D28" s="3">
-        <v>25.936936200374</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" s="3">
-        <v>4.79128264161059</v>
-      </c>
-      <c r="D29" s="3">
-        <v>28.1381015898811</v>
+      <c r="C29" s="2">
+        <v>4.7912826416105903</v>
+      </c>
+      <c r="D29" s="2">
+        <v>28.138101589881099</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection/>
-  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>